--- a/check_question_addition_uji_coba_entity.xlsx
+++ b/check_question_addition_uji_coba_entity.xlsx
@@ -10,7 +10,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="from gemini for testing entity" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Sheet5" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="163">
   <si>
     <t xml:space="preserve">kalimat</t>
   </si>
@@ -30,82 +32,172 @@
     <t xml:space="preserve">intent</t>
   </si>
   <si>
+    <t xml:space="preserve">Siapa pelanggan yang sering di bulan maret 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INT_RANKING_PELANGGAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kenapa emangnnya?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INT_TANYA_ALASAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hadiah apa yang cocok </t>
+  </si>
+  <si>
+    <t xml:space="preserve">INT_REKOMENDASI_HADIAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siapa pelanggan terbaik bulan ini?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siapa pelanggan paling rajin laundry bulan ini?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berikan 10 pelanggan terbaik bulan Mei.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siapa pelanggan yang paling sering cuci selama 3 bulan terakhir?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siapa pelanggan yang paling sering transaksi tahun ini?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelanggan yang jarang cuci bulan Maret siapa saja?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siapa pelanggan yang biasa saja dalam dua bulan terakhir?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tampilkan pelanggan terbaik bulan Januari sampai Maret.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berikan lima pelanggan dengan transaksi paling banyak bulan ini.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelanggan yang rajin cuci di bulan April dan Mei siapa?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kenapa pelanggan tersebut menjadi peringkat pertama?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mengapa Diana menjadi pelanggan terbaik?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apa alasan pelanggan itu berada di posisi pertama?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kok pelanggan ini bisa masuk ranking?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jelaskan alasan peringkat pelanggan tersebut.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadiah apa yang cocok untuk pelanggan terbaik?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reward apa yang sebaiknya diberikan kepada pelanggan ini?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menurutmu hadiah apa yang cocok untuk mereka?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalau pelanggan ini diberi hadiah, enaknya apa?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadiah yang sesuai untuk 10 pelanggan terbaik apa saja?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Berikan 10 pelanggan terbaik di 3 bulan ini</t>
   </si>
   <si>
-    <t xml:space="preserve">INT_RANKING_PELANGGAN</t>
+    <t xml:space="preserve">Berikan 5 pelanggan yang jarang cuci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pelanggan yang sering cuci di bulan mei siapa</t>
   </si>
   <si>
     <t xml:space="preserve">Berikan 6 pelanggan yang jarang cuci di dua bulan terahir ini</t>
   </si>
   <si>
-    <t xml:space="preserve">Berikan 5 pelanggan yang jarang cuci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kok pelanggan ini bisa masuk ranking?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INT_TANYA_ALASAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siapa pelanggan terbaik bulan ini?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siapa pelanggan paling rajin laundry bulan ini?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berikan 10 pelanggan terbaik bulan Mei.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siapa pelanggan yang paling sering cuci selama 3 bulan terakhir?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siapa pelanggan yang paling sering transaksi tahun ini?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelanggan yang jarang cuci bulan Maret siapa saja?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siapa pelanggan yang biasa saja dalam dua bulan terakhir?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tampilkan pelanggan terbaik bulan Januari sampai Maret.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berikan lima pelanggan dengan transaksi paling banyak bulan ini.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelanggan yang rajin cuci di bulan April dan Mei siapa?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kenapa pelanggan tersebut menjadi peringkat pertama?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mengapa Diana menjadi pelanggan terbaik?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apa alasan pelanggan itu berada di posisi pertama?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jelaskan alasan peringkat pelanggan tersebut.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadiah apa yang cocok untuk pelanggan terbaik?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INT_REKOMENDASI_HADIAH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reward apa yang sebaiknya diberikan kepada pelanggan ini?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menurutmu hadiah apa yang cocok untuk mereka?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalau pelanggan ini diberi hadiah, enaknya apa?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadiah yang sesuai untuk 10 pelanggan terbaik apa saja?</t>
+    <t xml:space="preserve">Siapa saja top 5 customer bulan januari kemarin?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tampilkan 3 pelanggan paling aktif minggu ini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siapa 10 pelanggan dengan prioritas utama tahun ini?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tunjukkan 7 pelanggan yang pasif di bulan april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berikan daftar 5 pelanggan teratas untuk cuci setrika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siapa saja pelanggan yang rajin laundry di semester ini?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tampilkan top 3 pelanggan laundry kiloan bulan lalu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelanggan yang kurang aktif di 4 minggu terakhir siapa saja?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berikan 12 pelanggan unggulan periode sekarang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siapa top customer untuk layanan satuan di bulan juni?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelanggan yang jarang datang selama tahun 2026 siapa?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tampilkan 8 pelanggan paling setia banget saat ini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cari 5 pelanggan terendah transaksi cuci keringnya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siapa 10 pelanggan favorit di bulan maret sampai mei?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berikan 4 pelanggan terbaik laundry periode berjalan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siapa pelanggan yang tidak aktif di dua bulan terakhir?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tampilkan 15 pelanggan dengan omset tertinggi bulan ini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urutkan 5 pelanggan terbaik dari bulan 4 sampai 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siapa customer paling loyal di minggu lalu?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berikan 3 top customer yang jarang cuci setrika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tampilkan pelanggan terbaik nomor satu hari ini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siapa 7 pelanggan paling sepi transaksinya di bulan februari?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berikan 10 pelanggan prioritas untuk laundry kiloan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siapa saja top 5 pelanggan berdasarkan frekuensi terbanyak?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tunjukkan 6 customer yang kurang aktif cuci baju</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siapa 8 pelanggan teratas sepanjang tahun ini?</t>
   </si>
   <si>
     <t xml:space="preserve">No</t>
@@ -529,7 +621,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -542,10 +634,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -554,19 +642,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -782,24 +866,20 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3"/>
@@ -810,44 +890,17 @@
       <c r="B7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5"/>
-    </row>
+      <c r="A8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="12.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -887,19 +940,19 @@
   <dimension ref="A1:B21"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.76"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+    <row r="1" customFormat="false" ht="13.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="47.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -907,7 +960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -915,7 +968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="47.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
@@ -923,7 +976,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
@@ -931,7 +984,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -939,7 +992,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -947,7 +1000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -955,7 +1008,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -963,7 +1016,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>16</v>
       </c>
@@ -971,7 +1024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>17</v>
       </c>
@@ -979,84 +1032,84 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="47.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1075,24 +1128,295 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34.71"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F51"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>32</v>
+      <c r="A1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1100,12 +1424,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+        <v>63</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="3" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="104.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1113,12 +1437,12 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
+        <v>65</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
       <c r="E3" s="3" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="104.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1126,12 +1450,12 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+        <v>67</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
       <c r="E4" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1139,12 +1463,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
+        <v>69</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
       <c r="E5" s="3" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1152,12 +1476,12 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+        <v>71</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
       <c r="E6" s="3" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1165,12 +1489,12 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
+        <v>73</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
       <c r="E7" s="3" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="93.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1178,12 +1502,12 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+        <v>75</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
       <c r="E8" s="3" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="93.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1191,12 +1515,12 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
+        <v>77</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
       <c r="E9" s="3" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1204,12 +1528,12 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+        <v>79</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
       <c r="E10" s="3" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1217,12 +1541,12 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
+        <v>81</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
       <c r="E11" s="3" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1230,12 +1554,12 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
+        <v>83</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
       <c r="E12" s="3" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1243,12 +1567,12 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
+        <v>85</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
       <c r="E13" s="3" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="93.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1256,12 +1580,12 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
+        <v>87</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
       <c r="E14" s="3" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1269,12 +1593,12 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
       <c r="E15" s="3" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1282,12 +1606,12 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
+        <v>91</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
       <c r="E16" s="3" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1295,12 +1619,12 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
+        <v>93</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
       <c r="E17" s="3" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1308,12 +1632,12 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
+        <v>95</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
       <c r="E18" s="3" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1321,12 +1645,12 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
+        <v>97</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
       <c r="E19" s="3" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1334,12 +1658,12 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
+        <v>99</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
       <c r="E20" s="3" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1347,12 +1671,12 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="8" t="s">
-        <v>72</v>
+        <v>101</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="6" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="93.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1360,12 +1684,12 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="8" t="s">
-        <v>74</v>
+        <v>103</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="6" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1373,12 +1697,12 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="9" t="s">
-        <v>76</v>
+        <v>105</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="7" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1386,12 +1710,12 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="9" t="s">
-        <v>78</v>
+        <v>107</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="7" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1399,12 +1723,12 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="9" t="s">
-        <v>80</v>
+        <v>109</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="7" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1412,12 +1736,12 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="9" t="s">
-        <v>82</v>
+        <v>111</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="7" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1425,12 +1749,12 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="9" t="s">
-        <v>84</v>
+        <v>113</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="7" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="93.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1438,12 +1762,12 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="9" t="s">
-        <v>86</v>
+        <v>115</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="7" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1451,12 +1775,12 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="9" t="s">
-        <v>88</v>
+        <v>117</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="7" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1464,12 +1788,12 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="9" t="s">
-        <v>90</v>
+        <v>119</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="7" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1477,12 +1801,12 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="9" t="s">
-        <v>92</v>
+        <v>121</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="7" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1490,12 +1814,12 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="9" t="s">
-        <v>94</v>
+        <v>123</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="7" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1503,12 +1827,12 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="9" t="s">
-        <v>96</v>
+        <v>125</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="7" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="93.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1516,12 +1840,12 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="9" t="s">
-        <v>98</v>
+        <v>127</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="7" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="93.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1529,12 +1853,12 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="9" t="s">
-        <v>100</v>
+        <v>129</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="7" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1542,12 +1866,12 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="9" t="s">
-        <v>102</v>
+        <v>131</v>
+      </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="7" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="104.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1555,12 +1879,12 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
+        <v>133</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
       <c r="E37" s="3" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="93.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1568,12 +1892,12 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
+        <v>135</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
       <c r="E38" s="3" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1581,12 +1905,12 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
+        <v>137</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
       <c r="E39" s="3" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="93.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1594,12 +1918,12 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
+        <v>139</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
       <c r="E40" s="3" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="93.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1607,12 +1931,12 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
+        <v>141</v>
+      </c>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
       <c r="E41" s="3" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="93.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1620,12 +1944,12 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
+        <v>143</v>
+      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
       <c r="E42" s="3" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="116.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1633,12 +1957,12 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
+        <v>145</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
       <c r="E43" s="3" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1646,12 +1970,12 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
+        <v>147</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
       <c r="E44" s="3" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="93.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1659,12 +1983,12 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
+        <v>149</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
       <c r="E45" s="3" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1672,12 +1996,12 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
+        <v>151</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
       <c r="E46" s="3" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="81.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1685,12 +2009,12 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
+        <v>153</v>
+      </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
       <c r="E47" s="3" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="93.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1698,12 +2022,12 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
+        <v>155</v>
+      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
       <c r="E48" s="3" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="104.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1711,12 +2035,12 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
+        <v>157</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
       <c r="E49" s="3" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1724,12 +2048,12 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
+        <v>159</v>
+      </c>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
       <c r="E50" s="3" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="93.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1737,12 +2061,79 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="F51" s="3"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="47.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="70.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="47.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="47.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="47.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
